--- a/bokslut_2025/Palteboken_ekonomi_2025.xlsx
+++ b/bokslut_2025/Palteboken_ekonomi_2025.xlsx
@@ -1,40 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkrogh/palteboken/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642B8DE9-67E0-0E46-9896-40675D5F1CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="20860" yWindow="620" windowWidth="23760" windowHeight="24100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Balans 2024" sheetId="1" r:id="rId1"/>
-    <sheet name="Result 2024" sheetId="2" r:id="rId2"/>
+    <sheet name="Balans" sheetId="1" r:id="rId5"/>
+    <sheet name="Result" sheetId="2" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
   <si>
     <t>Balansräkning</t>
   </si>
@@ -112,10 +90,13 @@
     <t>Konto</t>
   </si>
   <si>
+    <t>År 2025</t>
+  </si>
+  <si>
     <t>Utfall</t>
   </si>
   <si>
-    <t>År 2024</t>
+    <t>År 2026</t>
   </si>
   <si>
     <t>Budget</t>
@@ -193,32 +174,35 @@
     <t>Årsavgift:</t>
   </si>
   <si>
+    <t>Obetalde årsavgifter</t>
+  </si>
+  <si>
+    <t>Saldo Bankkonto 2023-01-01</t>
+  </si>
+  <si>
     <t>Saldo Bankkonto 2024-01-01</t>
-  </si>
-  <si>
-    <t>Saldo Bankkonto 2025-01-01</t>
-  </si>
-  <si>
-    <t>År 2025</t>
-  </si>
-  <si>
-    <t>12-31-24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot; kr&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot; kr&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="59" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="60" formatCode="#,##0&quot; kr&quot;"/>
+    <numFmt numFmtId="61" formatCode="#,##0.00&quot; kr&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="12"/>
@@ -226,20 +210,25 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <i/>
+      <b val="1"/>
+      <i val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -253,37 +242,6 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -300,7 +258,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -368,87 +326,100 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="59" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="60" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="61" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="60" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="60" fontId="6" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,85 +428,24 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFAAAAAA"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="ff00ff00"/>
+      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffff00"/>
+      <rgbColor rgb="ffff00ff"/>
+      <rgbColor rgb="ff00ffff"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffffffff"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -737,7 +647,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -755,7 +665,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -784,7 +694,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -809,7 +719,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -834,7 +744,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -859,7 +769,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -884,7 +794,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -909,7 +819,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -934,7 +844,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -959,7 +869,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -984,7 +894,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -997,15 +907,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1022,7 +926,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1040,7 +944,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1065,7 +969,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1090,7 +994,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1115,7 +1019,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1140,7 +1044,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1165,7 +1069,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1190,7 +1094,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1215,7 +1119,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1240,7 +1144,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1265,7 +1169,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1278,15 +1182,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1300,7 +1198,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1318,7 +1216,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1347,7 +1245,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1372,7 +1270,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1397,7 +1295,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1422,7 +1320,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1447,7 +1345,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1472,7 +1370,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1497,7 +1395,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1522,7 +1420,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1547,7 +1445,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1560,562 +1458,609 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.25" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="22.5" style="1" customWidth="1"/>
-    <col min="2" max="8" width="10.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="1"/>
+    <col min="2" max="10" width="10.8516" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="33"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="34"/>
-    </row>
-    <row r="3" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="34"/>
-    </row>
-    <row r="4" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="34"/>
-    </row>
-    <row r="5" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="3" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" ht="14.6" customHeight="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" ht="14.6" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" ht="14.6" customHeight="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" ht="14.6" customHeight="1">
+      <c r="A5" t="s" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>43100</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>43465</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>43830</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>44196</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>44561</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>44926</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="5">
         <v>45291</v>
       </c>
-      <c r="I5" s="35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="34"/>
-    </row>
-    <row r="7" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="3" t="s">
+      <c r="I5" s="5">
+        <v>45657</v>
+      </c>
+      <c r="J5" s="5">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="6" ht="14.6" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" ht="14.6" customHeight="1">
+      <c r="A7" t="s" s="4">
         <v>2</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>20000</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>18000</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>24500</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
         <v>10500</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>10500</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>17500</v>
       </c>
-      <c r="I7" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="34"/>
-    </row>
-    <row r="9" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="3" t="s">
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="8" ht="14.6" customHeight="1">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" ht="14.6" customHeight="1">
+      <c r="A9" t="s" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="6">
         <v>87980</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>91570</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
         <v>86837</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="6">
         <v>114070</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="6">
         <v>95984</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <v>83255</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="6">
         <v>63975</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="6">
         <v>64395</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="34"/>
-    </row>
-    <row r="11" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="3" t="s">
+      <c r="J9" s="6">
+        <v>38345</v>
+      </c>
+    </row>
+    <row r="10" ht="14.6" customHeight="1">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" ht="14.6" customHeight="1">
+      <c r="A11" t="s" s="4">
         <v>4</v>
       </c>
-      <c r="B11" s="5" cm="1">
+      <c r="B11" s="6" cm="1">
         <f t="array" ref="B11">B7+B9</f>
         <v>107980</v>
       </c>
-      <c r="C11" s="5" cm="1">
+      <c r="C11" s="6" cm="1">
         <f t="array" ref="C11">C7+C9</f>
         <v>109570</v>
       </c>
-      <c r="D11" s="5" cm="1">
+      <c r="D11" s="6" cm="1">
         <f t="array" ref="D11">D7+D9</f>
         <v>111337</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="6">
         <v>114070</v>
       </c>
-      <c r="F11" s="5" cm="1">
+      <c r="F11" s="6" cm="1">
         <f t="array" ref="F11">F7+F9</f>
         <v>106484</v>
       </c>
-      <c r="G11" s="5" cm="1">
+      <c r="G11" s="6" cm="1">
         <f t="array" ref="G11">G7+G9</f>
         <v>93755</v>
       </c>
-      <c r="H11" s="5" cm="1">
+      <c r="H11" s="6" cm="1">
         <f t="array" ref="H11">H7+H9</f>
         <v>81475</v>
       </c>
-      <c r="I11" s="34">
-        <f>I7+I9</f>
+      <c r="I11" s="6" cm="1">
+        <f t="array" ref="I11">I7+I9</f>
         <v>64395</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="34"/>
-    </row>
-    <row r="13" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="34"/>
-    </row>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="3" t="s">
+      <c r="J11" s="6" cm="1">
+        <f t="array" ref="J11">J7+J9</f>
+        <v>50345</v>
+      </c>
+    </row>
+    <row r="12" ht="14.6" customHeight="1">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" ht="14.6" customHeight="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" ht="14.6" customHeight="1">
+      <c r="A14" t="s" s="4">
         <v>5</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>43100</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>43465</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>43830</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>44196</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>44561</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>44926</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="5">
         <v>45291</v>
       </c>
-      <c r="I14" s="35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="34"/>
-    </row>
-    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="3" t="s">
+      <c r="I14" s="5">
+        <v>45657</v>
+      </c>
+      <c r="J14" s="5">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="15" ht="14.6" customHeight="1">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" ht="14.6" customHeight="1">
+      <c r="A16" t="s" s="4">
         <v>6</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="34"/>
-    </row>
-    <row r="17" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="34"/>
-    </row>
-    <row r="18" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="3" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" ht="14.6" customHeight="1">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" ht="14.6" customHeight="1">
+      <c r="A18" t="s" s="4">
         <v>7</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="34"/>
-    </row>
-    <row r="19" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="3" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" ht="14.6" customHeight="1">
+      <c r="A19" t="s" s="4">
         <v>8</v>
       </c>
-      <c r="B19" s="5">
-        <v>0</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="3" t="s">
+      <c r="B19" s="6">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="14.6" customHeight="1">
+      <c r="A20" t="s" s="4">
         <v>9</v>
       </c>
-      <c r="B20" s="5" cm="1">
+      <c r="B20" s="6" cm="1">
         <f t="array" ref="B20">B19</f>
         <v>0</v>
       </c>
-      <c r="C20" s="5">
-        <v>0</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="34"/>
-    </row>
-    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="3" t="s">
+      <c r="C20" s="6">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="14.6" customHeight="1">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" ht="14.6" customHeight="1">
+      <c r="A22" t="s" s="4">
         <v>10</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="34"/>
-    </row>
-    <row r="23" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="3" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" ht="14.6" customHeight="1">
+      <c r="A23" t="s" s="4">
         <v>11</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="6">
         <v>65148</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="6">
         <v>107980</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="6">
         <v>109570</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="6">
         <v>111337</v>
       </c>
-      <c r="F23" s="5" cm="1">
+      <c r="F23" s="6" cm="1">
         <f t="array" ref="F23">E25</f>
         <v>114070</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="6">
         <v>106484</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="6">
         <v>93755</v>
       </c>
-      <c r="I23" s="34">
-        <f>H25</f>
+      <c r="I23" s="6">
         <v>81475</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="3" t="s">
+      <c r="J23" s="6">
+        <v>64393</v>
+      </c>
+    </row>
+    <row r="24" ht="14.6" customHeight="1">
+      <c r="A24" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="6">
         <v>42832</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="6">
         <v>1590</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="6">
         <v>1767</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="6">
         <v>2733</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="6">
         <v>-7586</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="6">
         <v>-12729</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="6">
         <v>-12280</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="6">
         <v>-17082</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="3" t="s">
+      <c r="J24" s="6">
+        <v>-14049</v>
+      </c>
+    </row>
+    <row r="25" ht="14.6" customHeight="1">
+      <c r="A25" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="B25" s="5" cm="1">
+      <c r="B25" s="6" cm="1">
         <f t="array" ref="B25">B23+B24</f>
         <v>107980</v>
       </c>
-      <c r="C25" s="5" cm="1">
+      <c r="C25" s="6" cm="1">
         <f t="array" ref="C25">C23+C24</f>
         <v>109570</v>
       </c>
-      <c r="D25" s="5" cm="1">
+      <c r="D25" s="6" cm="1">
         <f t="array" ref="D25">D23+D24</f>
         <v>111337</v>
       </c>
-      <c r="E25" s="5" cm="1">
+      <c r="E25" s="6" cm="1">
         <f t="array" ref="E25">E23+E24</f>
         <v>114070</v>
       </c>
-      <c r="F25" s="5" cm="1">
+      <c r="F25" s="6" cm="1">
         <f t="array" ref="F25">F23+F24</f>
         <v>106484</v>
       </c>
-      <c r="G25" s="5" cm="1">
+      <c r="G25" s="6" cm="1">
         <f t="array" ref="G25">G23+G24</f>
         <v>93755</v>
       </c>
-      <c r="H25" s="5" cm="1">
+      <c r="H25" s="6" cm="1">
         <f t="array" ref="H25">H23+H24</f>
         <v>81475</v>
       </c>
-      <c r="I25" s="34">
-        <f>I23+I24</f>
+      <c r="I25" s="6" cm="1">
+        <f t="array" ref="I25">I23+I24</f>
         <v>64393</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="34"/>
-    </row>
-    <row r="27" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="3" t="s">
+      <c r="J25" s="6" cm="1">
+        <f t="array" ref="J25">J23+J24</f>
+        <v>50344</v>
+      </c>
+    </row>
+    <row r="26" ht="14.6" customHeight="1">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" ht="14.6" customHeight="1">
+      <c r="A27" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="B27" s="5" cm="1">
+      <c r="B27" s="6" cm="1">
         <f t="array" ref="B27">B20+B25</f>
         <v>107980</v>
       </c>
-      <c r="C27" s="5" cm="1">
+      <c r="C27" s="6" cm="1">
         <f t="array" ref="C27">C20+C25</f>
         <v>109570</v>
       </c>
-      <c r="D27" s="5" cm="1">
+      <c r="D27" s="6" cm="1">
         <f t="array" ref="D27">D20+D25</f>
         <v>111337</v>
       </c>
-      <c r="E27" s="5" cm="1">
+      <c r="E27" s="6" cm="1">
         <f t="array" ref="E27">E20+E25</f>
         <v>114070</v>
       </c>
-      <c r="F27" s="5" cm="1">
+      <c r="F27" s="6" cm="1">
         <f t="array" ref="F27">F20+F25</f>
         <v>106484</v>
       </c>
-      <c r="G27" s="5" cm="1">
+      <c r="G27" s="6" cm="1">
         <f t="array" ref="G27">G20+G25</f>
         <v>93755</v>
       </c>
-      <c r="H27" s="5" cm="1">
+      <c r="H27" s="6" cm="1">
         <f t="array" ref="H27">H20+H25</f>
         <v>81475</v>
       </c>
-      <c r="I27" s="36">
-        <f>I20+I25</f>
+      <c r="I27" s="6" cm="1">
+        <f t="array" ref="I27">I20+I25</f>
         <v>64393</v>
       </c>
+      <c r="J27" s="6" cm="1">
+        <f t="array" ref="J27">J20+J25</f>
+        <v>50344</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0" right="0" top="0.39410000000000001" bottom="0.39410000000000001" header="0" footer="0"/>
-  <pageSetup pageOrder="overThenDown" orientation="portrait"/>
+  <pageMargins left="0" right="0" top="0.3941" bottom="0.3941" header="0" footer="0"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="overThenDown"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Arial,Regular"&amp;11&amp;K000000Balans 2020</oddHeader>
     <oddFooter>&amp;C&amp;"Arial,Regular"&amp;11&amp;K000000Page &amp;P</oddFooter>
@@ -2124,505 +2069,500 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.15"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.45" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="9.85156" style="7" customWidth="1"/>
+    <col min="2" max="2" width="40.3516" style="7" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" customWidth="1"/>
+    <col min="4" max="4" width="15.8516" style="7" customWidth="1"/>
+    <col min="5" max="5" width="24" style="7" customWidth="1"/>
+    <col min="6" max="6" width="12.6719" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.85156" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6"/>
-      <c r="B1" s="7" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="8"/>
+      <c r="B1" t="s" s="9">
         <v>15</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="10"/>
+      <c r="B2" t="s" s="11">
         <v>16</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="s" s="12">
         <v>17</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="28" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" t="s" s="12">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="28" t="s">
+      <c r="E3" s="13"/>
+      <c r="F3" t="s" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" t="s" s="14">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s" s="15">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s" s="15">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s" s="15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="17">
+        <v>5050</v>
+      </c>
+      <c r="B6" t="s" s="15">
+        <v>23</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="17">
+        <v>5060</v>
+      </c>
+      <c r="B7" t="s" s="15">
+        <v>24</v>
+      </c>
+      <c r="C7" s="16">
+        <v>1200</v>
+      </c>
+      <c r="D7" s="16">
+        <v>1400</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="16">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="17">
+        <v>5090</v>
+      </c>
+      <c r="B8" t="s" s="15">
+        <v>25</v>
+      </c>
+      <c r="C8" s="16">
+        <v>29000</v>
+      </c>
+      <c r="D8" s="16">
+        <v>29057</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="16">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="17">
+        <v>5100</v>
+      </c>
+      <c r="B9" t="s" s="15">
+        <v>26</v>
+      </c>
+      <c r="C9" s="16">
+        <v>8000</v>
+      </c>
+      <c r="D9" s="16">
+        <v>7770</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="16">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="17">
+        <v>5105</v>
+      </c>
+      <c r="B10" t="s" s="14">
+        <v>27</v>
+      </c>
+      <c r="C10" s="16">
+        <v>5000</v>
+      </c>
+      <c r="D10" s="16">
+        <v>5094</v>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="16">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="17">
+        <v>5320</v>
+      </c>
+      <c r="B11" t="s" s="15">
+        <v>28</v>
+      </c>
+      <c r="C11" s="16">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="17">
+        <v>5350</v>
+      </c>
+      <c r="B12" t="s" s="15">
+        <v>29</v>
+      </c>
+      <c r="C12" s="16">
+        <v>16000</v>
+      </c>
+      <c r="D12" s="16">
+        <v>17729</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="16">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="17">
+        <v>5365</v>
+      </c>
+      <c r="B13" t="s" s="15">
+        <v>30</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="16"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="17">
+        <v>5370</v>
+      </c>
+      <c r="B14" t="s" s="15">
+        <v>31</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="17">
+        <v>5395</v>
+      </c>
+      <c r="B15" t="s" s="15">
+        <v>32</v>
+      </c>
+      <c r="C15" s="16">
+        <v>0</v>
+      </c>
+      <c r="D15" s="16">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="17">
+        <v>5400</v>
+      </c>
+      <c r="B16" t="s" s="15">
+        <v>33</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="16"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="17">
+        <v>7100</v>
+      </c>
+      <c r="B17" t="s" s="15">
+        <v>34</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="16"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="17">
+        <v>7110</v>
+      </c>
+      <c r="B18" t="s" s="15">
+        <v>35</v>
+      </c>
+      <c r="C18" s="16">
+        <v>10000</v>
+      </c>
+      <c r="D18" s="16">
+        <v>9000</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="16">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="17">
+        <v>7120</v>
+      </c>
+      <c r="B19" t="s" s="15">
+        <v>36</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="16"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="17">
+        <v>7130</v>
+      </c>
+      <c r="B20" t="s" s="15">
+        <v>37</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="17">
+        <v>7140</v>
+      </c>
+      <c r="B21" t="s" s="15">
+        <v>38</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="16"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="17">
+        <v>8000</v>
+      </c>
+      <c r="B22" t="s" s="15">
+        <v>39</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="16"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="17">
+        <v>8801</v>
+      </c>
+      <c r="B23" t="s" s="15">
+        <v>40</v>
+      </c>
+      <c r="C23" s="16">
+        <v>0</v>
+      </c>
+      <c r="D23" s="16">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13"/>
+      <c r="F23" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="17">
+        <v>3740</v>
+      </c>
+      <c r="B24" t="s" s="15">
+        <v>41</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16">
+        <v>-1</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="16"/>
+    </row>
+    <row r="25" ht="14.6" customHeight="1">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="8"/>
+      <c r="B26" t="s" s="21">
+        <v>42</v>
+      </c>
+      <c r="C26" s="22" cm="1">
+        <f t="array" ref="C26">SUM(C6:C23)</f>
+        <v>69200</v>
+      </c>
+      <c r="D26" s="22" cm="1">
+        <f t="array" ref="D26">SUM(D6:D24)+E31</f>
+        <v>70049</v>
+      </c>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22" cm="1">
+        <f t="array" ref="F26">SUM(F6:F23)</f>
+        <v>72400</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="8"/>
+      <c r="B27" t="s" s="21">
+        <v>43</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="22" cm="1">
+        <f t="array" ref="D27">D30-D26</f>
+        <v>-14049</v>
+      </c>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" t="s" s="23">
+        <v>44</v>
+      </c>
+      <c r="F28" s="22" cm="1">
+        <f t="array" ref="F28">F26/14</f>
+        <v>5171.428571428570</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="8"/>
+      <c r="B29" t="s" s="21">
+        <v>45</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25">
+        <v>4000</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="8"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25" cm="1">
+        <f t="array" ref="D30">D29*14+E29+E32</f>
+        <v>56000</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="8"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="8"/>
+      <c r="B32" t="s" s="21">
+        <v>46</v>
+      </c>
+      <c r="C32" s="24">
+        <v>12000</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="8"/>
+      <c r="B33" t="s" s="21">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="15">
-        <v>5050</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="14">
-        <v>0</v>
-      </c>
-      <c r="D6" s="14">
-        <v>0</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="15">
-        <v>5060</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="14">
-        <v>1200</v>
-      </c>
-      <c r="D7" s="14">
-        <v>1200</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="14">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="15">
-        <v>5090</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="14">
-        <v>28800</v>
-      </c>
-      <c r="D8" s="14">
-        <v>28803</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="14">
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="15">
-        <v>5100</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="14">
-        <v>8000</v>
-      </c>
-      <c r="D9" s="14">
-        <v>6544</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="14">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="15">
-        <v>5105</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="14">
-        <v>5000</v>
-      </c>
-      <c r="D10" s="14">
-        <v>9625</v>
-      </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="14">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="15">
-        <v>5320</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="14">
-        <v>0</v>
-      </c>
-      <c r="D11" s="14">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="15">
-        <v>5350</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="14">
-        <v>18000</v>
-      </c>
-      <c r="D12" s="14">
-        <v>15412</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="14">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="15">
-        <v>5365</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="15">
-        <v>5370</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="15">
-        <v>5395</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="14">
-        <v>0</v>
-      </c>
-      <c r="D15" s="14">
-        <v>0</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="15">
-        <v>5400</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="14"/>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="15">
-        <v>7100</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="15">
-        <v>7110</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="14">
-        <v>5000</v>
-      </c>
-      <c r="D18" s="14">
-        <v>4500</v>
-      </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="14">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="15">
-        <v>7120</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="15">
-        <v>7130</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="14"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="15">
-        <v>7140</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="15">
-        <v>8000</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="14"/>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="15">
-        <v>8801</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="14">
-        <v>0</v>
-      </c>
-      <c r="D23" s="14">
-        <v>0</v>
-      </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="15">
-        <v>3740</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14">
-        <v>-2</v>
-      </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="14"/>
-    </row>
-    <row r="25" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="6"/>
-      <c r="B26" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="20" cm="1">
-        <f t="array" ref="C26">SUM(C6:C23)</f>
-        <v>66000</v>
-      </c>
-      <c r="D26" s="20" cm="1">
-        <f t="array" ref="D26">SUM(D6:D24)+E31</f>
-        <v>66082</v>
-      </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20" cm="1">
-        <f t="array" ref="F26">SUM(F6:F23)</f>
-        <v>69200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="6"/>
-      <c r="B27" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="20" cm="1">
-        <f t="array" ref="D27">D30-D26</f>
-        <v>-17082</v>
-      </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="26" cm="1">
-        <f t="array" ref="F28">F26/14</f>
-        <v>4942.8571428571431</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="6"/>
-      <c r="B29" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="23">
-        <v>3500</v>
-      </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="6"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="23" cm="1">
-        <f t="array" ref="D30">D29*14+E29+E32</f>
-        <v>49000</v>
-      </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="6"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="6"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="6"/>
-      <c r="B33" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="20">
-        <v>63975</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="6"/>
-      <c r="B34" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="20">
+      <c r="C33" s="22">
         <v>64394</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="6"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="8"/>
+      <c r="B34" t="s" s="27">
+        <v>48</v>
+      </c>
+      <c r="C34" s="22">
+        <v>38345</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="8"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1.3936999999999999" bottom="1.3936999999999999" header="1" footer="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1.3937" bottom="1.3937" header="1" footer="1"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
